--- a/data/file/template_uuck.xlsx
+++ b/data/file/template_uuck.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Aryax punya\2026\KKA VAB\Aplikasi\imbalan-pasca-kerja-app\data\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Kerjaan Arya\KKA VAB\Aplikasi\imbalan-pasca-kerja-app\data\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF26BFD5-21D2-4DD2-AA94-EB6C3013FC9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7251A1B-E8A6-4173-B055-624CA0D8D83F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9AC3ECB3-0DA7-48EF-8B11-9B69DBBACB0E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AC3ECB3-0DA7-48EF-8B11-9B69DBBACB0E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>Pesangon</t>
   </si>
@@ -50,23 +50,18 @@
   <si>
     <t>mk</t>
   </si>
+  <si>
+    <t>Keluar</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,19 +118,19 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Comma [0] 9 2" xfId="1" xr:uid="{3AA96A0C-1829-4F63-AF52-242965A42A0E}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -448,23 +443,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F897658-CB39-4EE0-BD5D-358A4D71BD04}">
-  <dimension ref="P1:W420"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="P1:X420"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="14" width="0" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5546875" customWidth="1"/>
-    <col min="23" max="23" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" customWidth="1"/>
+    <col min="23" max="23" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.28515625" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="16:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="16:24" x14ac:dyDescent="0.25">
       <c r="Q1" t="s">
         <v>0</v>
       </c>
       <c r="R1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="X1"/>
+    </row>
+    <row r="2" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P2" t="s">
         <v>1</v>
       </c>
@@ -474,8 +471,9 @@
       <c r="R2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="X2"/>
+    </row>
+    <row r="3" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P3" t="s">
         <v>2</v>
       </c>
@@ -485,8 +483,9 @@
       <c r="R3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="X3"/>
+    </row>
+    <row r="4" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P4" s="1" t="s">
         <v>3</v>
       </c>
@@ -496,8 +495,9 @@
       <c r="R4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="X4"/>
+    </row>
+    <row r="5" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P5" t="s">
         <v>4</v>
       </c>
@@ -510,8 +510,9 @@
       <c r="S5">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="6" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="X5"/>
+    </row>
+    <row r="6" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P6" s="2" t="s">
         <v>7</v>
       </c>
@@ -525,10 +526,13 @@
         <v>3</v>
       </c>
       <c r="W6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="X6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="16:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P7" s="3">
         <v>0</v>
       </c>
@@ -554,9 +558,12 @@
         <f>(Q7*$Q$4+R7*$R$4)*(1+$S$5)</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="W7" s="5"/>
-    </row>
-    <row r="8" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W7" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="X7"/>
+    </row>
+    <row r="8" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P8" s="3">
         <f>0.1+P7</f>
         <v>0.1</v>
@@ -583,9 +590,12 @@
         <f t="shared" ref="V8:V71" si="3">(Q8*$Q$4+R8*$R$4)*(1+$S$5)</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="W8" s="5"/>
-    </row>
-    <row r="9" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W8" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="X8"/>
+    </row>
+    <row r="9" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P9" s="3">
         <f t="shared" ref="P9:P72" si="4">0.1+P8</f>
         <v>0.2</v>
@@ -612,9 +622,12 @@
         <f t="shared" si="3"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="W9" s="5"/>
-    </row>
-    <row r="10" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W9" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="X9"/>
+    </row>
+    <row r="10" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P10" s="3">
         <f t="shared" si="4"/>
         <v>0.30000000000000004</v>
@@ -641,9 +654,12 @@
         <f t="shared" si="3"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="W10" s="5"/>
-    </row>
-    <row r="11" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W10" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="X10"/>
+    </row>
+    <row r="11" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P11" s="3">
         <f t="shared" si="4"/>
         <v>0.4</v>
@@ -670,9 +686,12 @@
         <f t="shared" si="3"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="W11" s="5"/>
-    </row>
-    <row r="12" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W11" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="X11"/>
+    </row>
+    <row r="12" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P12" s="3">
         <f t="shared" si="4"/>
         <v>0.5</v>
@@ -699,9 +718,12 @@
         <f t="shared" si="3"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="W12" s="5"/>
-    </row>
-    <row r="13" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W12" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="X12"/>
+    </row>
+    <row r="13" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P13" s="3">
         <f t="shared" si="4"/>
         <v>0.6</v>
@@ -728,9 +750,12 @@
         <f t="shared" si="3"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="W13" s="5"/>
-    </row>
-    <row r="14" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W13" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="X13"/>
+    </row>
+    <row r="14" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P14" s="3">
         <f t="shared" si="4"/>
         <v>0.7</v>
@@ -757,9 +782,12 @@
         <f t="shared" si="3"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="W14" s="5"/>
-    </row>
-    <row r="15" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W14" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="X14"/>
+    </row>
+    <row r="15" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P15" s="3">
         <f t="shared" si="4"/>
         <v>0.79999999999999993</v>
@@ -786,9 +814,12 @@
         <f t="shared" si="3"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="W15" s="5"/>
-    </row>
-    <row r="16" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W15" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="X15"/>
+    </row>
+    <row r="16" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P16" s="3">
         <f t="shared" si="4"/>
         <v>0.89999999999999991</v>
@@ -815,9 +846,12 @@
         <f t="shared" si="3"/>
         <v>2.2999999999999998</v>
       </c>
-      <c r="W16" s="5"/>
-    </row>
-    <row r="17" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W16" s="5">
+        <v>0.15</v>
+      </c>
+      <c r="X16"/>
+    </row>
+    <row r="17" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P17" s="3">
         <f t="shared" si="4"/>
         <v>0.99999999999999989</v>
@@ -845,10 +879,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="W17" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+      <c r="X17"/>
+    </row>
+    <row r="18" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P18" s="3">
         <f t="shared" si="4"/>
         <v>1.0999999999999999</v>
@@ -876,10 +911,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="W18" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+      <c r="X18"/>
+    </row>
+    <row r="19" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P19" s="3">
         <f t="shared" si="4"/>
         <v>1.2</v>
@@ -907,10 +943,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="W19" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+      <c r="X19"/>
+    </row>
+    <row r="20" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P20" s="3">
         <f t="shared" si="4"/>
         <v>1.3</v>
@@ -938,10 +975,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="W20" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+      <c r="X20"/>
+    </row>
+    <row r="21" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P21" s="3">
         <f t="shared" si="4"/>
         <v>1.4000000000000001</v>
@@ -969,10 +1007,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="W21" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+      <c r="X21"/>
+    </row>
+    <row r="22" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P22" s="3">
         <f t="shared" si="4"/>
         <v>1.5000000000000002</v>
@@ -1000,10 +1039,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="W22" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+      <c r="X22"/>
+    </row>
+    <row r="23" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P23" s="3">
         <f t="shared" si="4"/>
         <v>1.6000000000000003</v>
@@ -1031,10 +1071,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="W23" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+      <c r="X23"/>
+    </row>
+    <row r="24" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P24" s="3">
         <f t="shared" si="4"/>
         <v>1.7000000000000004</v>
@@ -1062,10 +1103,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="W24" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+      <c r="X24"/>
+    </row>
+    <row r="25" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P25" s="3">
         <f t="shared" si="4"/>
         <v>1.8000000000000005</v>
@@ -1093,10 +1135,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="W25" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+      <c r="X25"/>
+    </row>
+    <row r="26" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P26" s="3">
         <f t="shared" si="4"/>
         <v>1.9000000000000006</v>
@@ -1124,10 +1167,11 @@
         <v>4.5999999999999996</v>
       </c>
       <c r="W26" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="27" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+      <c r="X26"/>
+    </row>
+    <row r="27" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P27" s="3">
         <f t="shared" si="4"/>
         <v>2.0000000000000004</v>
@@ -1155,10 +1199,11 @@
         <v>6.8999999999999995</v>
       </c>
       <c r="W27" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="28" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="X27"/>
+    </row>
+    <row r="28" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P28" s="3">
         <f t="shared" si="4"/>
         <v>2.1000000000000005</v>
@@ -1186,10 +1231,11 @@
         <v>6.8999999999999995</v>
       </c>
       <c r="W28" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="29" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="X28"/>
+    </row>
+    <row r="29" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P29" s="3">
         <f t="shared" si="4"/>
         <v>2.2000000000000006</v>
@@ -1217,10 +1263,11 @@
         <v>6.8999999999999995</v>
       </c>
       <c r="W29" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="X29"/>
+    </row>
+    <row r="30" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P30" s="3">
         <f t="shared" si="4"/>
         <v>2.3000000000000007</v>
@@ -1248,10 +1295,11 @@
         <v>6.8999999999999995</v>
       </c>
       <c r="W30" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="X30"/>
+    </row>
+    <row r="31" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P31" s="3">
         <f t="shared" si="4"/>
         <v>2.4000000000000008</v>
@@ -1279,10 +1327,11 @@
         <v>6.8999999999999995</v>
       </c>
       <c r="W31" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="32" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="X31"/>
+    </row>
+    <row r="32" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P32" s="3">
         <f t="shared" si="4"/>
         <v>2.5000000000000009</v>
@@ -1310,10 +1359,11 @@
         <v>6.8999999999999995</v>
       </c>
       <c r="W32" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="X32"/>
+    </row>
+    <row r="33" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P33" s="3">
         <f t="shared" si="4"/>
         <v>2.600000000000001</v>
@@ -1341,10 +1391,11 @@
         <v>6.8999999999999995</v>
       </c>
       <c r="W33" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="34" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="X33"/>
+    </row>
+    <row r="34" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P34" s="3">
         <f t="shared" si="4"/>
         <v>2.7000000000000011</v>
@@ -1372,10 +1423,11 @@
         <v>6.8999999999999995</v>
       </c>
       <c r="W34" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="35" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="X34"/>
+    </row>
+    <row r="35" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P35" s="3">
         <f t="shared" si="4"/>
         <v>2.8000000000000012</v>
@@ -1403,10 +1455,11 @@
         <v>6.8999999999999995</v>
       </c>
       <c r="W35" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="36" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="X35"/>
+    </row>
+    <row r="36" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P36" s="3">
         <f t="shared" si="4"/>
         <v>2.9000000000000012</v>
@@ -1434,10 +1487,11 @@
         <v>6.8999999999999995</v>
       </c>
       <c r="W36" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="37" spans="16:23" x14ac:dyDescent="0.3">
+        <v>0.44999999999999996</v>
+      </c>
+      <c r="X36"/>
+    </row>
+    <row r="37" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P37" s="3">
         <f t="shared" si="4"/>
         <v>3.0000000000000013</v>
@@ -1464,11 +1518,14 @@
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
-      <c r="W37" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W37" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="X37" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P38" s="3">
         <f t="shared" si="4"/>
         <v>3.1000000000000014</v>
@@ -1495,11 +1552,14 @@
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
-      <c r="W38" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W38" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="X38" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P39" s="3">
         <f t="shared" si="4"/>
         <v>3.2000000000000015</v>
@@ -1526,11 +1586,14 @@
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
-      <c r="W39" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W39" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="X39" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P40" s="3">
         <f t="shared" si="4"/>
         <v>3.3000000000000016</v>
@@ -1557,11 +1620,14 @@
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
-      <c r="W40" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W40" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="X40" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P41" s="3">
         <f t="shared" si="4"/>
         <v>3.4000000000000017</v>
@@ -1588,11 +1654,14 @@
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
-      <c r="W41" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W41" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="X41" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P42" s="3">
         <f t="shared" si="4"/>
         <v>3.5000000000000018</v>
@@ -1619,11 +1688,14 @@
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
-      <c r="W42" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W42" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="X42" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P43" s="3">
         <f t="shared" si="4"/>
         <v>3.6000000000000019</v>
@@ -1650,11 +1722,14 @@
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
-      <c r="W43" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W43" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="X43" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P44" s="3">
         <f t="shared" si="4"/>
         <v>3.700000000000002</v>
@@ -1681,11 +1756,14 @@
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
-      <c r="W44" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W44" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="X44" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P45" s="3">
         <f t="shared" si="4"/>
         <v>3.800000000000002</v>
@@ -1712,11 +1790,14 @@
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
-      <c r="W45" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W45" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="X45" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P46" s="3">
         <f t="shared" si="4"/>
         <v>3.9000000000000021</v>
@@ -1743,11 +1824,14 @@
         <f t="shared" si="3"/>
         <v>11.5</v>
       </c>
-      <c r="W46" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W46" s="5">
+        <v>1.4</v>
+      </c>
+      <c r="X46" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P47" s="3">
         <f t="shared" si="4"/>
         <v>4.0000000000000018</v>
@@ -1774,11 +1858,14 @@
         <f t="shared" si="3"/>
         <v>13.799999999999999</v>
       </c>
-      <c r="W47" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W47" s="5">
+        <v>1.55</v>
+      </c>
+      <c r="X47" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P48" s="3">
         <f t="shared" si="4"/>
         <v>4.1000000000000014</v>
@@ -1805,11 +1892,14 @@
         <f t="shared" si="3"/>
         <v>13.799999999999999</v>
       </c>
-      <c r="W48" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W48" s="5">
+        <v>1.55</v>
+      </c>
+      <c r="X48" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P49" s="3">
         <f t="shared" si="4"/>
         <v>4.2000000000000011</v>
@@ -1836,11 +1926,14 @@
         <f t="shared" si="3"/>
         <v>13.799999999999999</v>
       </c>
-      <c r="W49" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W49" s="5">
+        <v>1.55</v>
+      </c>
+      <c r="X49" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P50" s="3">
         <f t="shared" si="4"/>
         <v>4.3000000000000007</v>
@@ -1867,11 +1960,14 @@
         <f t="shared" si="3"/>
         <v>13.799999999999999</v>
       </c>
-      <c r="W50" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W50" s="5">
+        <v>1.55</v>
+      </c>
+      <c r="X50" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P51" s="3">
         <f t="shared" si="4"/>
         <v>4.4000000000000004</v>
@@ -1898,11 +1994,14 @@
         <f t="shared" si="3"/>
         <v>13.799999999999999</v>
       </c>
-      <c r="W51" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W51" s="5">
+        <v>1.55</v>
+      </c>
+      <c r="X51" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P52" s="3">
         <f t="shared" si="4"/>
         <v>4.5</v>
@@ -1929,11 +2028,14 @@
         <f t="shared" si="3"/>
         <v>13.799999999999999</v>
       </c>
-      <c r="W52" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W52" s="5">
+        <v>1.55</v>
+      </c>
+      <c r="X52" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P53" s="3">
         <f t="shared" si="4"/>
         <v>4.5999999999999996</v>
@@ -1960,11 +2062,14 @@
         <f t="shared" si="3"/>
         <v>13.799999999999999</v>
       </c>
-      <c r="W53" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W53" s="5">
+        <v>1.55</v>
+      </c>
+      <c r="X53" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P54" s="3">
         <f t="shared" si="4"/>
         <v>4.6999999999999993</v>
@@ -1991,11 +2096,14 @@
         <f t="shared" si="3"/>
         <v>13.799999999999999</v>
       </c>
-      <c r="W54" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W54" s="5">
+        <v>1.55</v>
+      </c>
+      <c r="X54" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P55" s="3">
         <f t="shared" si="4"/>
         <v>4.7999999999999989</v>
@@ -2022,11 +2130,14 @@
         <f t="shared" si="3"/>
         <v>13.799999999999999</v>
       </c>
-      <c r="W55" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W55" s="5">
+        <v>1.55</v>
+      </c>
+      <c r="X55" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P56" s="3">
         <f t="shared" si="4"/>
         <v>4.8999999999999986</v>
@@ -2053,11 +2164,14 @@
         <f t="shared" si="3"/>
         <v>13.799999999999999</v>
       </c>
-      <c r="W56" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W56" s="5">
+        <v>1.55</v>
+      </c>
+      <c r="X56" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P57" s="3">
         <f t="shared" si="4"/>
         <v>4.9999999999999982</v>
@@ -2084,11 +2198,14 @@
         <f t="shared" si="3"/>
         <v>16.099999999999998</v>
       </c>
-      <c r="W57" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W57" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X57" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P58" s="3">
         <f t="shared" si="4"/>
         <v>5.0999999999999979</v>
@@ -2115,11 +2232,14 @@
         <f t="shared" si="3"/>
         <v>16.099999999999998</v>
       </c>
-      <c r="W58" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W58" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X58" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P59" s="3">
         <f t="shared" si="4"/>
         <v>5.1999999999999975</v>
@@ -2146,11 +2266,14 @@
         <f t="shared" si="3"/>
         <v>16.099999999999998</v>
       </c>
-      <c r="W59" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W59" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X59" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P60" s="3">
         <f t="shared" si="4"/>
         <v>5.2999999999999972</v>
@@ -2177,11 +2300,14 @@
         <f t="shared" si="3"/>
         <v>16.099999999999998</v>
       </c>
-      <c r="W60" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W60" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X60" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P61" s="3">
         <f t="shared" si="4"/>
         <v>5.3999999999999968</v>
@@ -2208,11 +2334,14 @@
         <f t="shared" si="3"/>
         <v>16.099999999999998</v>
       </c>
-      <c r="W61" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W61" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X61" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P62" s="3">
         <f t="shared" si="4"/>
         <v>5.4999999999999964</v>
@@ -2239,11 +2368,14 @@
         <f t="shared" si="3"/>
         <v>16.099999999999998</v>
       </c>
-      <c r="W62" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W62" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X62" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P63" s="3">
         <f t="shared" si="4"/>
         <v>5.5999999999999961</v>
@@ -2270,11 +2402,14 @@
         <f t="shared" si="3"/>
         <v>16.099999999999998</v>
       </c>
-      <c r="W63" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W63" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X63" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P64" s="3">
         <f t="shared" si="4"/>
         <v>5.6999999999999957</v>
@@ -2301,11 +2436,14 @@
         <f t="shared" si="3"/>
         <v>16.099999999999998</v>
       </c>
-      <c r="W64" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W64" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X64" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P65" s="3">
         <f t="shared" si="4"/>
         <v>5.7999999999999954</v>
@@ -2332,11 +2470,14 @@
         <f t="shared" si="3"/>
         <v>16.099999999999998</v>
       </c>
-      <c r="W65" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W65" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X65" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P66" s="3">
         <f t="shared" si="4"/>
         <v>5.899999999999995</v>
@@ -2363,11 +2504,14 @@
         <f t="shared" si="3"/>
         <v>16.099999999999998</v>
       </c>
-      <c r="W66" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W66" s="5">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X66" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P67" s="3">
         <f t="shared" si="4"/>
         <v>5.9999999999999947</v>
@@ -2394,11 +2538,14 @@
         <f t="shared" si="3"/>
         <v>19.549999999999997</v>
       </c>
-      <c r="W67" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W67" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="X67" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P68" s="3">
         <f t="shared" si="4"/>
         <v>6.0999999999999943</v>
@@ -2425,11 +2572,14 @@
         <f t="shared" si="3"/>
         <v>19.549999999999997</v>
       </c>
-      <c r="W68" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W68" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="X68" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P69" s="3">
         <f t="shared" si="4"/>
         <v>6.199999999999994</v>
@@ -2456,11 +2606,14 @@
         <f t="shared" si="3"/>
         <v>19.549999999999997</v>
       </c>
-      <c r="W69" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W69" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="X69" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P70" s="3">
         <f t="shared" si="4"/>
         <v>6.2999999999999936</v>
@@ -2487,11 +2640,14 @@
         <f t="shared" si="3"/>
         <v>19.549999999999997</v>
       </c>
-      <c r="W70" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="71" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W70" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="X70" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P71" s="3">
         <f t="shared" si="4"/>
         <v>6.3999999999999932</v>
@@ -2518,11 +2674,14 @@
         <f t="shared" si="3"/>
         <v>19.549999999999997</v>
       </c>
-      <c r="W71" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W71" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="X71" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P72" s="3">
         <f t="shared" si="4"/>
         <v>6.4999999999999929</v>
@@ -2549,11 +2708,14 @@
         <f t="shared" ref="V72:V135" si="8">(Q72*$Q$4+R72*$R$4)*(1+$S$5)</f>
         <v>19.549999999999997</v>
       </c>
-      <c r="W72" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W72" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="X72" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P73" s="3">
         <f t="shared" ref="P73:P136" si="9">0.1+P72</f>
         <v>6.5999999999999925</v>
@@ -2580,11 +2742,14 @@
         <f t="shared" si="8"/>
         <v>19.549999999999997</v>
       </c>
-      <c r="W73" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W73" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="X73" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P74" s="3">
         <f t="shared" si="9"/>
         <v>6.6999999999999922</v>
@@ -2611,11 +2776,14 @@
         <f t="shared" si="8"/>
         <v>19.549999999999997</v>
       </c>
-      <c r="W74" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W74" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="X74" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P75" s="3">
         <f t="shared" si="9"/>
         <v>6.7999999999999918</v>
@@ -2642,11 +2810,14 @@
         <f t="shared" si="8"/>
         <v>19.549999999999997</v>
       </c>
-      <c r="W75" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W75" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="X75" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P76" s="3">
         <f t="shared" si="9"/>
         <v>6.8999999999999915</v>
@@ -2673,11 +2844,14 @@
         <f t="shared" si="8"/>
         <v>19.549999999999997</v>
       </c>
-      <c r="W76" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W76" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="X76" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P77" s="3">
         <f t="shared" si="9"/>
         <v>6.9999999999999911</v>
@@ -2704,11 +2878,14 @@
         <f t="shared" si="8"/>
         <v>21.849999999999998</v>
       </c>
-      <c r="W77" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W77" s="5">
+        <v>2.65</v>
+      </c>
+      <c r="X77" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P78" s="3">
         <f t="shared" si="9"/>
         <v>7.0999999999999908</v>
@@ -2735,11 +2912,14 @@
         <f t="shared" si="8"/>
         <v>21.849999999999998</v>
       </c>
-      <c r="W78" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W78" s="5">
+        <v>2.65</v>
+      </c>
+      <c r="X78" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P79" s="3">
         <f t="shared" si="9"/>
         <v>7.1999999999999904</v>
@@ -2766,11 +2946,14 @@
         <f t="shared" si="8"/>
         <v>21.849999999999998</v>
       </c>
-      <c r="W79" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W79" s="5">
+        <v>2.65</v>
+      </c>
+      <c r="X79" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P80" s="3">
         <f t="shared" si="9"/>
         <v>7.2999999999999901</v>
@@ -2797,11 +2980,14 @@
         <f t="shared" si="8"/>
         <v>21.849999999999998</v>
       </c>
-      <c r="W80" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W80" s="5">
+        <v>2.65</v>
+      </c>
+      <c r="X80" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P81" s="3">
         <f t="shared" si="9"/>
         <v>7.3999999999999897</v>
@@ -2828,11 +3014,14 @@
         <f t="shared" si="8"/>
         <v>21.849999999999998</v>
       </c>
-      <c r="W81" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W81" s="5">
+        <v>2.65</v>
+      </c>
+      <c r="X81" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P82" s="3">
         <f t="shared" si="9"/>
         <v>7.4999999999999893</v>
@@ -2859,11 +3048,14 @@
         <f t="shared" si="8"/>
         <v>21.849999999999998</v>
       </c>
-      <c r="W82" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W82" s="5">
+        <v>2.65</v>
+      </c>
+      <c r="X82" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P83" s="3">
         <f t="shared" si="9"/>
         <v>7.599999999999989</v>
@@ -2890,11 +3082,14 @@
         <f t="shared" si="8"/>
         <v>21.849999999999998</v>
       </c>
-      <c r="W83" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W83" s="5">
+        <v>2.65</v>
+      </c>
+      <c r="X83" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P84" s="3">
         <f t="shared" si="9"/>
         <v>7.6999999999999886</v>
@@ -2921,11 +3116,14 @@
         <f t="shared" si="8"/>
         <v>21.849999999999998</v>
       </c>
-      <c r="W84" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W84" s="5">
+        <v>2.65</v>
+      </c>
+      <c r="X84" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P85" s="3">
         <f t="shared" si="9"/>
         <v>7.7999999999999883</v>
@@ -2952,11 +3150,14 @@
         <f t="shared" si="8"/>
         <v>21.849999999999998</v>
       </c>
-      <c r="W85" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W85" s="5">
+        <v>2.65</v>
+      </c>
+      <c r="X85" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P86" s="3">
         <f t="shared" si="9"/>
         <v>7.8999999999999879</v>
@@ -2983,11 +3184,14 @@
         <f t="shared" si="8"/>
         <v>21.849999999999998</v>
       </c>
-      <c r="W86" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W86" s="5">
+        <v>2.65</v>
+      </c>
+      <c r="X86" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P87" s="3">
         <f t="shared" si="9"/>
         <v>7.9999999999999876</v>
@@ -3014,11 +3218,14 @@
         <f t="shared" si="8"/>
         <v>24.15</v>
       </c>
-      <c r="W87" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W87" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="X87" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P88" s="3">
         <f t="shared" si="9"/>
         <v>8.0999999999999872</v>
@@ -3045,11 +3252,14 @@
         <f t="shared" si="8"/>
         <v>24.15</v>
       </c>
-      <c r="W88" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W88" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="X88" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P89" s="3">
         <f t="shared" si="9"/>
         <v>8.1999999999999869</v>
@@ -3076,11 +3286,14 @@
         <f t="shared" si="8"/>
         <v>24.15</v>
       </c>
-      <c r="W89" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W89" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="X89" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P90" s="3">
         <f t="shared" si="9"/>
         <v>8.2999999999999865</v>
@@ -3107,11 +3320,14 @@
         <f t="shared" si="8"/>
         <v>24.15</v>
       </c>
-      <c r="W90" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="91" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W90" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="X90" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P91" s="3">
         <f t="shared" si="9"/>
         <v>8.3999999999999861</v>
@@ -3138,11 +3354,14 @@
         <f t="shared" si="8"/>
         <v>24.15</v>
       </c>
-      <c r="W91" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="92" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W91" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="X91" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P92" s="3">
         <f t="shared" si="9"/>
         <v>8.4999999999999858</v>
@@ -3169,11 +3388,14 @@
         <f t="shared" si="8"/>
         <v>24.15</v>
       </c>
-      <c r="W92" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W92" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="X92" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P93" s="3">
         <f t="shared" si="9"/>
         <v>8.5999999999999854</v>
@@ -3200,11 +3422,14 @@
         <f t="shared" si="8"/>
         <v>24.15</v>
       </c>
-      <c r="W93" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W93" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="X93" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P94" s="3">
         <f t="shared" si="9"/>
         <v>8.6999999999999851</v>
@@ -3231,11 +3456,14 @@
         <f t="shared" si="8"/>
         <v>24.15</v>
       </c>
-      <c r="W94" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W94" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="X94" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P95" s="3">
         <f t="shared" si="9"/>
         <v>8.7999999999999847</v>
@@ -3262,11 +3490,14 @@
         <f t="shared" si="8"/>
         <v>24.15</v>
       </c>
-      <c r="W95" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W95" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="X95" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P96" s="3">
         <f t="shared" si="9"/>
         <v>8.8999999999999844</v>
@@ -3293,11 +3524,14 @@
         <f t="shared" si="8"/>
         <v>24.15</v>
       </c>
-      <c r="W96" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W96" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="X96" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P97" s="3">
         <f t="shared" si="9"/>
         <v>8.999999999999984</v>
@@ -3324,11 +3558,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W97" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W97" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X97" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P98" s="3">
         <f t="shared" si="9"/>
         <v>9.0999999999999837</v>
@@ -3355,11 +3592,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W98" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W98" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X98" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P99" s="3">
         <f t="shared" si="9"/>
         <v>9.1999999999999833</v>
@@ -3386,11 +3626,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W99" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W99" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X99" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P100" s="3">
         <f t="shared" si="9"/>
         <v>9.2999999999999829</v>
@@ -3417,11 +3660,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W100" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W100" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X100" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P101" s="3">
         <f t="shared" si="9"/>
         <v>9.3999999999999826</v>
@@ -3448,11 +3694,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W101" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W101" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X101" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P102" s="3">
         <f t="shared" si="9"/>
         <v>9.4999999999999822</v>
@@ -3479,11 +3728,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W102" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W102" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X102" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P103" s="3">
         <f t="shared" si="9"/>
         <v>9.5999999999999819</v>
@@ -3510,11 +3762,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W103" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W103" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X103" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P104" s="3">
         <f t="shared" si="9"/>
         <v>9.6999999999999815</v>
@@ -3541,11 +3796,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W104" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W104" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X104" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P105" s="3">
         <f t="shared" si="9"/>
         <v>9.7999999999999812</v>
@@ -3572,11 +3830,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W105" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W105" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X105" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P106" s="3">
         <f t="shared" si="9"/>
         <v>9.8999999999999808</v>
@@ -3603,11 +3864,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W106" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W106" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X106" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P107" s="3">
         <f t="shared" si="9"/>
         <v>9.9999999999999805</v>
@@ -3634,11 +3898,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W107" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W107" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X107" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P108" s="3">
         <f t="shared" si="9"/>
         <v>10.09999999999998</v>
@@ -3665,11 +3932,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W108" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W108" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X108" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P109" s="3">
         <f t="shared" si="9"/>
         <v>10.19999999999998</v>
@@ -3696,11 +3966,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W109" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W109" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X109" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P110" s="3">
         <f t="shared" si="9"/>
         <v>10.299999999999979</v>
@@ -3727,11 +4000,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W110" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W110" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X110" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P111" s="3">
         <f t="shared" si="9"/>
         <v>10.399999999999979</v>
@@ -3758,11 +4034,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W111" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="112" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W111" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X111" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P112" s="3">
         <f t="shared" si="9"/>
         <v>10.499999999999979</v>
@@ -3789,11 +4068,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W112" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="113" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W112" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X112" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P113" s="3">
         <f t="shared" si="9"/>
         <v>10.599999999999978</v>
@@ -3820,11 +4102,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W113" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W113" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X113" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P114" s="3">
         <f t="shared" si="9"/>
         <v>10.699999999999978</v>
@@ -3851,11 +4136,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W114" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="115" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W114" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X114" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P115" s="3">
         <f t="shared" si="9"/>
         <v>10.799999999999978</v>
@@ -3882,11 +4170,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W115" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W115" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X115" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P116" s="3">
         <f t="shared" si="9"/>
         <v>10.899999999999977</v>
@@ -3913,11 +4204,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W116" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="117" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W116" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X116" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P117" s="3">
         <f t="shared" si="9"/>
         <v>10.999999999999977</v>
@@ -3944,11 +4238,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W117" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W117" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X117" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P118" s="3">
         <f t="shared" si="9"/>
         <v>11.099999999999977</v>
@@ -3975,11 +4272,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W118" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="119" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W118" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X118" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P119" s="3">
         <f t="shared" si="9"/>
         <v>11.199999999999976</v>
@@ -4006,11 +4306,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W119" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="120" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W119" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X119" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P120" s="3">
         <f t="shared" si="9"/>
         <v>11.299999999999976</v>
@@ -4037,11 +4340,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W120" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="121" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W120" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X120" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P121" s="3">
         <f t="shared" si="9"/>
         <v>11.399999999999975</v>
@@ -4068,11 +4374,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W121" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W121" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X121" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P122" s="3">
         <f t="shared" si="9"/>
         <v>11.499999999999975</v>
@@ -4099,11 +4408,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W122" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="123" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W122" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X122" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P123" s="3">
         <f t="shared" si="9"/>
         <v>11.599999999999975</v>
@@ -4130,11 +4442,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W123" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="124" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W123" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X123" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P124" s="3">
         <f t="shared" si="9"/>
         <v>11.699999999999974</v>
@@ -4161,11 +4476,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W124" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="125" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W124" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X124" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P125" s="3">
         <f t="shared" si="9"/>
         <v>11.799999999999974</v>
@@ -4192,11 +4510,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W125" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="126" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W125" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X125" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P126" s="3">
         <f t="shared" si="9"/>
         <v>11.899999999999974</v>
@@ -4223,11 +4544,14 @@
         <f t="shared" si="8"/>
         <v>25.299999999999997</v>
       </c>
-      <c r="W126" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="127" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W126" s="5">
+        <v>2.95</v>
+      </c>
+      <c r="X126" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P127" s="3">
         <f t="shared" si="9"/>
         <v>11.999999999999973</v>
@@ -4254,11 +4578,14 @@
         <f t="shared" si="8"/>
         <v>26.45</v>
       </c>
-      <c r="W127" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W127" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X127" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P128" s="3">
         <f t="shared" si="9"/>
         <v>12.099999999999973</v>
@@ -4285,11 +4612,14 @@
         <f t="shared" si="8"/>
         <v>26.45</v>
       </c>
-      <c r="W128" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="129" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W128" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X128" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P129" s="3">
         <f t="shared" si="9"/>
         <v>12.199999999999973</v>
@@ -4316,11 +4646,14 @@
         <f t="shared" si="8"/>
         <v>26.45</v>
       </c>
-      <c r="W129" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="130" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W129" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X129" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P130" s="3">
         <f t="shared" si="9"/>
         <v>12.299999999999972</v>
@@ -4347,11 +4680,14 @@
         <f t="shared" si="8"/>
         <v>26.45</v>
       </c>
-      <c r="W130" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="131" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W130" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X130" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P131" s="3">
         <f t="shared" si="9"/>
         <v>12.399999999999972</v>
@@ -4378,11 +4714,14 @@
         <f t="shared" si="8"/>
         <v>26.45</v>
       </c>
-      <c r="W131" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="132" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W131" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X131" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P132" s="3">
         <f t="shared" si="9"/>
         <v>12.499999999999972</v>
@@ -4409,11 +4748,14 @@
         <f t="shared" si="8"/>
         <v>26.45</v>
       </c>
-      <c r="W132" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="133" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W132" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X132" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P133" s="3">
         <f t="shared" si="9"/>
         <v>12.599999999999971</v>
@@ -4440,11 +4782,14 @@
         <f t="shared" si="8"/>
         <v>26.45</v>
       </c>
-      <c r="W133" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="134" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W133" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X133" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P134" s="3">
         <f t="shared" si="9"/>
         <v>12.699999999999971</v>
@@ -4471,11 +4816,14 @@
         <f t="shared" si="8"/>
         <v>26.45</v>
       </c>
-      <c r="W134" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="135" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W134" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X134" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P135" s="3">
         <f t="shared" si="9"/>
         <v>12.799999999999971</v>
@@ -4502,11 +4850,14 @@
         <f t="shared" si="8"/>
         <v>26.45</v>
       </c>
-      <c r="W135" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W135" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X135" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P136" s="3">
         <f t="shared" si="9"/>
         <v>12.89999999999997</v>
@@ -4533,11 +4884,14 @@
         <f t="shared" ref="V136:V199" si="13">(Q136*$Q$4+R136*$R$4)*(1+$S$5)</f>
         <v>26.45</v>
       </c>
-      <c r="W136" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W136" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X136" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P137" s="3">
         <f t="shared" ref="P137:P200" si="14">0.1+P136</f>
         <v>12.99999999999997</v>
@@ -4564,11 +4918,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W137" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="138" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W137" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X137" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P138" s="3">
         <f t="shared" si="14"/>
         <v>13.099999999999969</v>
@@ -4595,11 +4952,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W138" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="139" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W138" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X138" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P139" s="3">
         <f t="shared" si="14"/>
         <v>13.199999999999969</v>
@@ -4626,11 +4986,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W139" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="140" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W139" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X139" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P140" s="3">
         <f t="shared" si="14"/>
         <v>13.299999999999969</v>
@@ -4657,11 +5020,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W140" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="141" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W140" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X140" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P141" s="3">
         <f t="shared" si="14"/>
         <v>13.399999999999968</v>
@@ -4688,11 +5054,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W141" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="142" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W141" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X141" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P142" s="3">
         <f t="shared" si="14"/>
         <v>13.499999999999968</v>
@@ -4719,11 +5088,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W142" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="143" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W142" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X142" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P143" s="3">
         <f t="shared" si="14"/>
         <v>13.599999999999968</v>
@@ -4750,11 +5122,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W143" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="144" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W143" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X143" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P144" s="3">
         <f t="shared" si="14"/>
         <v>13.699999999999967</v>
@@ -4781,11 +5156,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W144" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="145" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W144" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X144" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P145" s="3">
         <f t="shared" si="14"/>
         <v>13.799999999999967</v>
@@ -4812,11 +5190,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W145" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="146" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W145" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X145" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P146" s="3">
         <f t="shared" si="14"/>
         <v>13.899999999999967</v>
@@ -4843,11 +5224,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W146" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="147" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W146" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X146" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P147" s="3">
         <f t="shared" si="14"/>
         <v>13.999999999999966</v>
@@ -4874,11 +5258,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W147" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="148" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W147" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X147" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P148" s="3">
         <f t="shared" si="14"/>
         <v>14.099999999999966</v>
@@ -4905,11 +5292,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W148" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="149" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W148" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X148" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P149" s="3">
         <f t="shared" si="14"/>
         <v>14.199999999999966</v>
@@ -4936,11 +5326,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W149" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="150" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W149" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X149" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P150" s="3">
         <f t="shared" si="14"/>
         <v>14.299999999999965</v>
@@ -4967,11 +5360,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W150" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="151" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W150" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X150" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P151" s="3">
         <f t="shared" si="14"/>
         <v>14.399999999999965</v>
@@ -4998,11 +5394,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W151" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="152" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W151" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X151" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P152" s="3">
         <f t="shared" si="14"/>
         <v>14.499999999999964</v>
@@ -5029,11 +5428,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W152" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="153" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W152" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X152" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P153" s="3">
         <f t="shared" si="14"/>
         <v>14.599999999999964</v>
@@ -5060,11 +5462,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W153" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="154" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W153" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X153" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P154" s="3">
         <f t="shared" si="14"/>
         <v>14.699999999999964</v>
@@ -5091,11 +5496,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W154" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="155" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W154" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X154" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P155" s="3">
         <f t="shared" si="14"/>
         <v>14.799999999999963</v>
@@ -5122,11 +5530,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W155" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="156" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W155" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X155" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P156" s="3">
         <f t="shared" si="14"/>
         <v>14.899999999999963</v>
@@ -5153,11 +5564,14 @@
         <f t="shared" si="13"/>
         <v>26.45</v>
       </c>
-      <c r="W156" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="157" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W156" s="5">
+        <v>3.1</v>
+      </c>
+      <c r="X156" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P157" s="3">
         <f t="shared" si="14"/>
         <v>14.999999999999963</v>
@@ -5184,11 +5598,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W157" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="158" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W157" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X157" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P158" s="3">
         <f t="shared" si="14"/>
         <v>15.099999999999962</v>
@@ -5215,11 +5632,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W158" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="159" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W158" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X158" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P159" s="3">
         <f t="shared" si="14"/>
         <v>15.199999999999962</v>
@@ -5246,11 +5666,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W159" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="160" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W159" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X159" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P160" s="3">
         <f t="shared" si="14"/>
         <v>15.299999999999962</v>
@@ -5277,11 +5700,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W160" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="161" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W160" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X160" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P161" s="3">
         <f t="shared" si="14"/>
         <v>15.399999999999961</v>
@@ -5308,11 +5734,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W161" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="162" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W161" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X161" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P162" s="3">
         <f t="shared" si="14"/>
         <v>15.499999999999961</v>
@@ -5339,11 +5768,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W162" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="163" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W162" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X162" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P163" s="3">
         <f t="shared" si="14"/>
         <v>15.599999999999961</v>
@@ -5370,11 +5802,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W163" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="164" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W163" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X163" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P164" s="3">
         <f t="shared" si="14"/>
         <v>15.69999999999996</v>
@@ -5401,11 +5836,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W164" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="165" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W164" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X164" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P165" s="3">
         <f t="shared" si="14"/>
         <v>15.79999999999996</v>
@@ -5432,11 +5870,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W165" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="166" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W165" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X165" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P166" s="3">
         <f t="shared" si="14"/>
         <v>15.899999999999959</v>
@@ -5463,11 +5904,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W166" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="167" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W166" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X166" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P167" s="3">
         <f t="shared" si="14"/>
         <v>15.999999999999959</v>
@@ -5494,11 +5938,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W167" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="168" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W167" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X167" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P168" s="3">
         <f t="shared" si="14"/>
         <v>16.099999999999959</v>
@@ -5525,11 +5972,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W168" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="169" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W168" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X168" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P169" s="3">
         <f t="shared" si="14"/>
         <v>16.19999999999996</v>
@@ -5556,11 +6006,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W169" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="170" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W169" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X169" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P170" s="3">
         <f t="shared" si="14"/>
         <v>16.299999999999962</v>
@@ -5587,11 +6040,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W170" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="171" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W170" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X170" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P171" s="3">
         <f t="shared" si="14"/>
         <v>16.399999999999963</v>
@@ -5618,11 +6074,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W171" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="172" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W171" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X171" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P172" s="3">
         <f t="shared" si="14"/>
         <v>16.499999999999964</v>
@@ -5649,11 +6108,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W172" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="173" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W172" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X172" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P173" s="3">
         <f t="shared" si="14"/>
         <v>16.599999999999966</v>
@@ -5680,11 +6142,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W173" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="174" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W173" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X173" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P174" s="3">
         <f t="shared" si="14"/>
         <v>16.699999999999967</v>
@@ -5711,11 +6176,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W174" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="175" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W174" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X174" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P175" s="3">
         <f t="shared" si="14"/>
         <v>16.799999999999969</v>
@@ -5742,11 +6210,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W175" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="176" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W175" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X175" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P176" s="3">
         <f t="shared" si="14"/>
         <v>16.89999999999997</v>
@@ -5773,11 +6244,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W176" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="177" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W176" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X176" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P177" s="3">
         <f t="shared" si="14"/>
         <v>16.999999999999972</v>
@@ -5804,11 +6278,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W177" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="178" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W177" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X177" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P178" s="3">
         <f t="shared" si="14"/>
         <v>17.099999999999973</v>
@@ -5835,11 +6312,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W178" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="179" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W178" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X178" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P179" s="3">
         <f t="shared" si="14"/>
         <v>17.199999999999974</v>
@@ -5866,11 +6346,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W179" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="180" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W179" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X179" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="180" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P180" s="3">
         <f t="shared" si="14"/>
         <v>17.299999999999976</v>
@@ -5897,11 +6380,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W180" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="181" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W180" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X180" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P181" s="3">
         <f t="shared" si="14"/>
         <v>17.399999999999977</v>
@@ -5928,11 +6414,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W181" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="182" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W181" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X181" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P182" s="3">
         <f t="shared" si="14"/>
         <v>17.499999999999979</v>
@@ -5959,11 +6448,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W182" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="183" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W182" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X182" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="183" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P183" s="3">
         <f t="shared" si="14"/>
         <v>17.59999999999998</v>
@@ -5990,11 +6482,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W183" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="184" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W183" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X183" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P184" s="3">
         <f t="shared" si="14"/>
         <v>17.699999999999982</v>
@@ -6021,11 +6516,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W184" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="185" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W184" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X184" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="185" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P185" s="3">
         <f t="shared" si="14"/>
         <v>17.799999999999983</v>
@@ -6052,11 +6550,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W185" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="186" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W185" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X185" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="186" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P186" s="3">
         <f t="shared" si="14"/>
         <v>17.899999999999984</v>
@@ -6083,11 +6584,14 @@
         <f t="shared" si="13"/>
         <v>27.599999999999998</v>
       </c>
-      <c r="W186" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="187" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W186" s="5">
+        <v>3.25</v>
+      </c>
+      <c r="X186" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="187" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P187" s="3">
         <f t="shared" si="14"/>
         <v>17.999999999999986</v>
@@ -6114,11 +6618,14 @@
         <f t="shared" si="13"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W187" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="188" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W187" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X187" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P188" s="3">
         <f t="shared" si="14"/>
         <v>18.099999999999987</v>
@@ -6145,11 +6652,14 @@
         <f t="shared" si="13"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W188" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="189" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W188" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X188" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P189" s="3">
         <f t="shared" si="14"/>
         <v>18.199999999999989</v>
@@ -6176,11 +6686,14 @@
         <f t="shared" si="13"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W189" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="190" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W189" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X189" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P190" s="3">
         <f t="shared" si="14"/>
         <v>18.29999999999999</v>
@@ -6207,11 +6720,14 @@
         <f t="shared" si="13"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W190" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="191" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W190" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X190" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P191" s="3">
         <f t="shared" si="14"/>
         <v>18.399999999999991</v>
@@ -6238,11 +6754,14 @@
         <f t="shared" si="13"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W191" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="192" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W191" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X191" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P192" s="3">
         <f t="shared" si="14"/>
         <v>18.499999999999993</v>
@@ -6269,11 +6788,14 @@
         <f t="shared" si="13"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W192" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="193" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W192" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X192" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P193" s="3">
         <f t="shared" si="14"/>
         <v>18.599999999999994</v>
@@ -6300,11 +6822,14 @@
         <f t="shared" si="13"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W193" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="194" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W193" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X193" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P194" s="3">
         <f t="shared" si="14"/>
         <v>18.699999999999996</v>
@@ -6331,11 +6856,14 @@
         <f t="shared" si="13"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W194" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="195" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W194" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X194" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="195" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P195" s="3">
         <f t="shared" si="14"/>
         <v>18.799999999999997</v>
@@ -6362,11 +6890,14 @@
         <f t="shared" si="13"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W195" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="196" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W195" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X195" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P196" s="3">
         <f t="shared" si="14"/>
         <v>18.899999999999999</v>
@@ -6393,11 +6924,14 @@
         <f t="shared" si="13"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W196" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="197" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W196" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X196" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P197" s="3">
         <f t="shared" si="14"/>
         <v>19</v>
@@ -6424,11 +6958,14 @@
         <f t="shared" si="13"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W197" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="198" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W197" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X197" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P198" s="3">
         <f t="shared" si="14"/>
         <v>19.100000000000001</v>
@@ -6455,11 +6992,14 @@
         <f t="shared" si="13"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W198" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="199" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W198" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X198" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P199" s="3">
         <f t="shared" si="14"/>
         <v>19.200000000000003</v>
@@ -6486,11 +7026,14 @@
         <f t="shared" si="13"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W199" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="200" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W199" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X199" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P200" s="3">
         <f t="shared" si="14"/>
         <v>19.300000000000004</v>
@@ -6517,11 +7060,14 @@
         <f t="shared" ref="V200:V263" si="18">(Q200*$Q$4+R200*$R$4)*(1+$S$5)</f>
         <v>28.749999999999996</v>
       </c>
-      <c r="W200" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="201" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W200" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X200" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P201" s="3">
         <f t="shared" ref="P201:P264" si="19">0.1+P200</f>
         <v>19.400000000000006</v>
@@ -6548,11 +7094,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W201" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="202" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W201" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X201" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="202" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P202" s="3">
         <f t="shared" si="19"/>
         <v>19.500000000000007</v>
@@ -6579,11 +7128,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W202" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="203" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W202" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X202" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="203" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P203" s="3">
         <f t="shared" si="19"/>
         <v>19.600000000000009</v>
@@ -6610,11 +7162,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W203" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="204" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W203" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X203" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="204" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P204" s="3">
         <f t="shared" si="19"/>
         <v>19.70000000000001</v>
@@ -6641,11 +7196,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W204" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="205" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W204" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X204" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P205" s="3">
         <f t="shared" si="19"/>
         <v>19.800000000000011</v>
@@ -6672,11 +7230,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W205" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="206" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W205" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X205" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="206" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P206" s="3">
         <f t="shared" si="19"/>
         <v>19.900000000000013</v>
@@ -6703,11 +7264,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W206" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="207" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W206" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X206" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="207" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P207" s="3">
         <f t="shared" si="19"/>
         <v>20.000000000000014</v>
@@ -6734,11 +7298,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W207" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="208" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W207" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X207" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P208" s="3">
         <f t="shared" si="19"/>
         <v>20.100000000000016</v>
@@ -6765,11 +7332,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W208" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="209" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W208" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X208" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="209" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P209" s="3">
         <f t="shared" si="19"/>
         <v>20.200000000000017</v>
@@ -6796,11 +7366,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W209" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="210" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W209" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X209" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="210" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P210" s="3">
         <f t="shared" si="19"/>
         <v>20.300000000000018</v>
@@ -6827,11 +7400,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W210" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="211" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W210" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X210" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="211" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P211" s="3">
         <f t="shared" si="19"/>
         <v>20.40000000000002</v>
@@ -6858,11 +7434,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W211" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="212" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W211" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X211" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P212" s="3">
         <f t="shared" si="19"/>
         <v>20.500000000000021</v>
@@ -6889,11 +7468,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W212" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="213" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W212" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X212" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P213" s="3">
         <f t="shared" si="19"/>
         <v>20.600000000000023</v>
@@ -6920,11 +7502,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W213" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="214" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W213" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X213" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P214" s="3">
         <f t="shared" si="19"/>
         <v>20.700000000000024</v>
@@ -6951,11 +7536,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W214" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="215" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W214" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X214" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P215" s="3">
         <f t="shared" si="19"/>
         <v>20.800000000000026</v>
@@ -6982,11 +7570,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W215" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="216" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W215" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X215" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="216" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P216" s="3">
         <f t="shared" si="19"/>
         <v>20.900000000000027</v>
@@ -7013,11 +7604,14 @@
         <f t="shared" si="18"/>
         <v>28.749999999999996</v>
       </c>
-      <c r="W216" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="217" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W216" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="X216" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P217" s="3">
         <f t="shared" si="19"/>
         <v>21.000000000000028</v>
@@ -7044,11 +7638,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W217" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="218" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W217" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X217" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="218" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P218" s="3">
         <f t="shared" si="19"/>
         <v>21.10000000000003</v>
@@ -7075,11 +7672,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W218" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="219" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W218" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X218" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="219" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P219" s="3">
         <f t="shared" si="19"/>
         <v>21.200000000000031</v>
@@ -7106,11 +7706,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W219" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="220" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W219" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X219" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P220" s="3">
         <f t="shared" si="19"/>
         <v>21.300000000000033</v>
@@ -7137,11 +7740,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W220" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="221" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W220" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X220" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="221" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P221" s="3">
         <f t="shared" si="19"/>
         <v>21.400000000000034</v>
@@ -7168,11 +7774,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W221" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="222" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W221" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X221" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="222" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P222" s="3">
         <f t="shared" si="19"/>
         <v>21.500000000000036</v>
@@ -7199,11 +7808,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W222" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="223" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W222" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X222" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="223" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P223" s="3">
         <f t="shared" si="19"/>
         <v>21.600000000000037</v>
@@ -7230,11 +7842,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W223" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="224" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W223" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X223" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="224" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P224" s="3">
         <f t="shared" si="19"/>
         <v>21.700000000000038</v>
@@ -7261,11 +7876,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W224" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="225" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W224" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X224" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="225" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P225" s="3">
         <f t="shared" si="19"/>
         <v>21.80000000000004</v>
@@ -7292,11 +7910,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W225" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="226" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W225" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X225" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="226" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P226" s="3">
         <f t="shared" si="19"/>
         <v>21.900000000000041</v>
@@ -7323,11 +7944,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W226" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="227" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W226" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X226" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="227" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P227" s="3">
         <f t="shared" si="19"/>
         <v>22.000000000000043</v>
@@ -7354,11 +7978,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W227" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="228" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W227" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X227" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="228" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P228" s="3">
         <f t="shared" si="19"/>
         <v>22.100000000000044</v>
@@ -7385,11 +8012,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W228" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="229" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W228" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X228" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="229" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P229" s="3">
         <f t="shared" si="19"/>
         <v>22.200000000000045</v>
@@ -7416,11 +8046,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W229" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="230" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W229" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X229" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="230" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P230" s="3">
         <f t="shared" si="19"/>
         <v>22.300000000000047</v>
@@ -7447,11 +8080,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W230" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="231" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W230" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X230" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="231" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P231" s="3">
         <f t="shared" si="19"/>
         <v>22.400000000000048</v>
@@ -7478,11 +8114,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W231" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="232" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W231" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X231" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="232" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P232" s="3">
         <f t="shared" si="19"/>
         <v>22.50000000000005</v>
@@ -7509,11 +8148,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W232" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="233" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W232" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X232" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="233" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P233" s="3">
         <f t="shared" si="19"/>
         <v>22.600000000000051</v>
@@ -7540,11 +8182,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W233" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="234" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W233" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X233" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P234" s="3">
         <f t="shared" si="19"/>
         <v>22.700000000000053</v>
@@ -7571,11 +8216,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W234" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="235" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W234" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X234" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="235" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P235" s="3">
         <f t="shared" si="19"/>
         <v>22.800000000000054</v>
@@ -7602,11 +8250,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W235" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="236" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W235" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X235" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="236" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P236" s="3">
         <f t="shared" si="19"/>
         <v>22.900000000000055</v>
@@ -7633,11 +8284,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W236" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="237" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W236" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X236" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="237" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P237" s="3">
         <f t="shared" si="19"/>
         <v>23.000000000000057</v>
@@ -7664,11 +8318,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W237" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="238" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W237" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X237" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="238" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P238" s="3">
         <f t="shared" si="19"/>
         <v>23.100000000000058</v>
@@ -7695,11 +8352,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W238" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="239" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W238" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X238" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="239" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P239" s="3">
         <f t="shared" si="19"/>
         <v>23.20000000000006</v>
@@ -7726,11 +8386,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W239" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="240" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W239" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X239" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P240" s="3">
         <f t="shared" si="19"/>
         <v>23.300000000000061</v>
@@ -7757,11 +8420,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W240" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="241" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W240" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X240" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="241" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P241" s="3">
         <f t="shared" si="19"/>
         <v>23.400000000000063</v>
@@ -7788,11 +8454,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W241" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="242" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W241" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X241" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="242" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P242" s="3">
         <f t="shared" si="19"/>
         <v>23.500000000000064</v>
@@ -7819,11 +8488,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W242" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="243" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W242" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X242" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="243" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P243" s="3">
         <f t="shared" si="19"/>
         <v>23.600000000000065</v>
@@ -7850,11 +8522,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W243" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="244" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W243" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X243" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="244" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P244" s="3">
         <f t="shared" si="19"/>
         <v>23.700000000000067</v>
@@ -7881,11 +8556,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W244" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="245" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W244" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X244" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="245" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P245" s="3">
         <f t="shared" si="19"/>
         <v>23.800000000000068</v>
@@ -7912,11 +8590,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W245" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="246" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W245" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X245" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="246" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P246" s="3">
         <f t="shared" si="19"/>
         <v>23.90000000000007</v>
@@ -7943,11 +8624,14 @@
         <f t="shared" si="18"/>
         <v>29.9</v>
       </c>
-      <c r="W246" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="247" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W246" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="X246" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="247" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P247" s="3">
         <f t="shared" si="19"/>
         <v>24.000000000000071</v>
@@ -7974,11 +8658,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W247" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="248" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W247" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X247" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="248" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P248" s="3">
         <f t="shared" si="19"/>
         <v>24.100000000000072</v>
@@ -8005,11 +8692,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W248" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="249" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W248" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X248" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="249" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P249" s="3">
         <f t="shared" si="19"/>
         <v>24.200000000000074</v>
@@ -8036,11 +8726,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W249" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="250" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W249" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X249" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="250" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P250" s="3">
         <f t="shared" si="19"/>
         <v>24.300000000000075</v>
@@ -8067,11 +8760,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W250" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="251" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W250" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X250" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="251" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P251" s="3">
         <f t="shared" si="19"/>
         <v>24.400000000000077</v>
@@ -8098,11 +8794,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W251" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="252" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W251" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X251" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="252" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P252" s="3">
         <f t="shared" si="19"/>
         <v>24.500000000000078</v>
@@ -8129,11 +8828,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W252" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="253" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W252" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X252" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="253" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P253" s="3">
         <f t="shared" si="19"/>
         <v>24.60000000000008</v>
@@ -8160,11 +8862,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W253" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="254" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W253" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X253" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="254" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P254" s="3">
         <f t="shared" si="19"/>
         <v>24.700000000000081</v>
@@ -8191,11 +8896,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W254" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="255" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W254" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X254" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="255" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P255" s="3">
         <f t="shared" si="19"/>
         <v>24.800000000000082</v>
@@ -8222,11 +8930,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W255" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="256" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W255" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X255" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="256" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P256" s="3">
         <f t="shared" si="19"/>
         <v>24.900000000000084</v>
@@ -8253,11 +8964,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W256" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="257" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W256" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X256" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="257" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P257" s="3">
         <f t="shared" si="19"/>
         <v>25.000000000000085</v>
@@ -8284,11 +8998,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W257" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="258" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W257" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X257" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="258" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P258" s="3">
         <f t="shared" si="19"/>
         <v>25.100000000000087</v>
@@ -8315,11 +9032,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W258" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="259" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W258" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X258" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="259" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P259" s="3">
         <f t="shared" si="19"/>
         <v>25.200000000000088</v>
@@ -8346,11 +9066,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W259" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="260" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W259" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X259" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="260" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P260" s="3">
         <f t="shared" si="19"/>
         <v>25.30000000000009</v>
@@ -8377,11 +9100,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W260" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="261" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W260" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X260" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="261" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P261" s="3">
         <f t="shared" si="19"/>
         <v>25.400000000000091</v>
@@ -8408,11 +9134,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W261" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="262" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W261" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X261" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="262" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P262" s="3">
         <f t="shared" si="19"/>
         <v>25.500000000000092</v>
@@ -8439,11 +9168,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W262" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="263" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W262" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X262" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="263" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P263" s="3">
         <f t="shared" si="19"/>
         <v>25.600000000000094</v>
@@ -8470,11 +9202,14 @@
         <f t="shared" si="18"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W263" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="264" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W263" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X263" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="264" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P264" s="3">
         <f t="shared" si="19"/>
         <v>25.700000000000095</v>
@@ -8501,11 +9236,14 @@
         <f t="shared" ref="V264:V327" si="23">(Q264*$Q$4+R264*$R$4)*(1+$S$5)</f>
         <v>32.199999999999996</v>
       </c>
-      <c r="W264" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="265" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W264" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X264" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="265" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P265" s="3">
         <f t="shared" ref="P265:P328" si="24">0.1+P264</f>
         <v>25.800000000000097</v>
@@ -8532,11 +9270,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W265" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="266" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W265" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X265" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="266" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P266" s="3">
         <f t="shared" si="24"/>
         <v>25.900000000000098</v>
@@ -8563,11 +9304,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W266" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="267" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W266" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X266" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="267" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P267" s="3">
         <f t="shared" si="24"/>
         <v>26.000000000000099</v>
@@ -8594,11 +9338,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W267" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="268" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W267" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X267" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="268" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P268" s="3">
         <f t="shared" si="24"/>
         <v>26.100000000000101</v>
@@ -8625,11 +9372,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W268" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="269" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W268" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X268" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="269" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P269" s="3">
         <f t="shared" si="24"/>
         <v>26.200000000000102</v>
@@ -8656,11 +9406,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W269" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="270" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W269" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X269" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="270" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P270" s="3">
         <f t="shared" si="24"/>
         <v>26.300000000000104</v>
@@ -8687,11 +9440,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W270" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="271" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W270" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X270" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="271" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P271" s="3">
         <f t="shared" si="24"/>
         <v>26.400000000000105</v>
@@ -8718,11 +9474,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W271" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="272" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W271" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X271" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="272" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P272" s="3">
         <f t="shared" si="24"/>
         <v>26.500000000000107</v>
@@ -8749,11 +9508,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W272" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="273" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W272" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X272" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="273" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P273" s="3">
         <f t="shared" si="24"/>
         <v>26.600000000000108</v>
@@ -8780,11 +9542,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W273" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="274" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W273" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X273" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="274" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P274" s="3">
         <f t="shared" si="24"/>
         <v>26.700000000000109</v>
@@ -8811,11 +9576,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W274" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="275" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W274" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X274" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="275" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P275" s="3">
         <f t="shared" si="24"/>
         <v>26.800000000000111</v>
@@ -8842,11 +9610,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W275" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="276" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W275" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X275" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="276" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P276" s="3">
         <f t="shared" si="24"/>
         <v>26.900000000000112</v>
@@ -8873,11 +9644,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W276" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="277" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W276" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X276" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="277" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P277" s="3">
         <f t="shared" si="24"/>
         <v>27.000000000000114</v>
@@ -8904,11 +9678,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W277" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="278" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W277" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X277" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="278" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P278" s="3">
         <f t="shared" si="24"/>
         <v>27.100000000000115</v>
@@ -8935,11 +9712,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W278" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="279" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W278" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X278" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="279" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P279" s="3">
         <f t="shared" si="24"/>
         <v>27.200000000000117</v>
@@ -8966,11 +9746,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W279" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="280" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W279" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X279" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="280" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P280" s="3">
         <f t="shared" si="24"/>
         <v>27.300000000000118</v>
@@ -8997,11 +9780,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W280" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="281" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W280" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X280" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="281" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P281" s="3">
         <f t="shared" si="24"/>
         <v>27.400000000000119</v>
@@ -9028,11 +9814,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W281" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="282" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W281" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X281" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="282" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P282" s="3">
         <f t="shared" si="24"/>
         <v>27.500000000000121</v>
@@ -9059,11 +9848,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W282" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="283" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W282" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X282" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="283" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P283" s="3">
         <f t="shared" si="24"/>
         <v>27.600000000000122</v>
@@ -9090,11 +9882,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W283" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="284" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W283" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X283" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="284" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P284" s="3">
         <f t="shared" si="24"/>
         <v>27.700000000000124</v>
@@ -9121,11 +9916,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W284" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="285" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W284" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X284" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="285" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P285" s="3">
         <f t="shared" si="24"/>
         <v>27.800000000000125</v>
@@ -9152,11 +9950,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W285" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="286" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W285" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X285" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="286" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P286" s="3">
         <f t="shared" si="24"/>
         <v>27.900000000000126</v>
@@ -9183,11 +9984,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W286" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="287" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W286" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X286" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="287" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P287" s="3">
         <f t="shared" si="24"/>
         <v>28.000000000000128</v>
@@ -9214,11 +10018,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W287" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="288" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W287" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X287" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="288" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P288" s="3">
         <f t="shared" si="24"/>
         <v>28.100000000000129</v>
@@ -9245,11 +10052,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W288" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="289" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W288" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X288" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="289" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P289" s="3">
         <f t="shared" si="24"/>
         <v>28.200000000000131</v>
@@ -9276,11 +10086,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W289" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="290" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W289" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X289" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="290" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P290" s="3">
         <f t="shared" si="24"/>
         <v>28.300000000000132</v>
@@ -9307,11 +10120,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W290" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="291" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W290" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X290" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="291" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P291" s="3">
         <f t="shared" si="24"/>
         <v>28.400000000000134</v>
@@ -9338,11 +10154,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W291" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="292" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W291" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X291" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="292" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P292" s="3">
         <f t="shared" si="24"/>
         <v>28.500000000000135</v>
@@ -9369,11 +10188,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W292" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="293" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W292" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X292" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="293" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P293" s="3">
         <f t="shared" si="24"/>
         <v>28.600000000000136</v>
@@ -9400,11 +10222,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W293" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="294" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W293" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X293" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="294" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P294" s="3">
         <f t="shared" si="24"/>
         <v>28.700000000000138</v>
@@ -9431,11 +10256,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W294" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="295" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W294" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X294" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="295" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P295" s="3">
         <f t="shared" si="24"/>
         <v>28.800000000000139</v>
@@ -9462,11 +10290,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W295" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="296" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W295" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X295" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="296" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P296" s="3">
         <f t="shared" si="24"/>
         <v>28.900000000000141</v>
@@ -9493,11 +10324,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W296" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="297" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W296" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X296" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="297" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P297" s="3">
         <f t="shared" si="24"/>
         <v>29.000000000000142</v>
@@ -9524,11 +10358,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W297" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="298" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W297" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X297" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="298" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P298" s="3">
         <f t="shared" si="24"/>
         <v>29.100000000000144</v>
@@ -9555,11 +10392,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W298" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="299" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W298" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X298" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="299" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P299" s="3">
         <f t="shared" si="24"/>
         <v>29.200000000000145</v>
@@ -9586,11 +10426,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W299" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="300" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W299" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X299" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="300" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P300" s="3">
         <f t="shared" si="24"/>
         <v>29.300000000000146</v>
@@ -9617,11 +10460,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W300" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="301" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W300" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X300" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="301" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P301" s="3">
         <f t="shared" si="24"/>
         <v>29.400000000000148</v>
@@ -9648,11 +10494,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W301" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="302" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W301" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X301" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="302" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P302" s="3">
         <f t="shared" si="24"/>
         <v>29.500000000000149</v>
@@ -9679,11 +10528,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W302" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="303" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W302" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X302" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="303" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P303" s="3">
         <f t="shared" si="24"/>
         <v>29.600000000000151</v>
@@ -9710,11 +10562,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W303" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="304" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W303" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X303" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="304" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P304" s="3">
         <f t="shared" si="24"/>
         <v>29.700000000000152</v>
@@ -9741,11 +10596,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W304" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="305" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W304" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X304" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="305" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P305" s="3">
         <f t="shared" si="24"/>
         <v>29.800000000000153</v>
@@ -9772,11 +10630,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W305" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="306" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W305" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X305" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="306" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P306" s="3">
         <f t="shared" si="24"/>
         <v>29.900000000000155</v>
@@ -9803,11 +10664,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W306" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="307" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W306" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X306" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="307" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P307" s="3">
         <f t="shared" si="24"/>
         <v>30.000000000000156</v>
@@ -9834,11 +10698,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W307" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="308" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W307" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X307" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="308" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P308" s="3">
         <f t="shared" si="24"/>
         <v>30.100000000000158</v>
@@ -9865,11 +10732,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W308" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="309" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W308" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X308" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="309" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P309" s="3">
         <f t="shared" si="24"/>
         <v>30.200000000000159</v>
@@ -9896,11 +10766,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W309" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="310" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W309" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X309" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="310" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P310" s="3">
         <f t="shared" si="24"/>
         <v>30.300000000000161</v>
@@ -9927,11 +10800,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W310" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="311" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W310" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X310" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="311" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P311" s="3">
         <f t="shared" si="24"/>
         <v>30.400000000000162</v>
@@ -9958,11 +10834,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W311" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="312" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W311" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X311" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="312" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P312" s="3">
         <f t="shared" si="24"/>
         <v>30.500000000000163</v>
@@ -9989,11 +10868,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W312" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="313" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W312" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X312" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="313" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P313" s="3">
         <f t="shared" si="24"/>
         <v>30.600000000000165</v>
@@ -10020,11 +10902,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W313" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="314" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W313" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X313" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="314" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P314" s="3">
         <f t="shared" si="24"/>
         <v>30.700000000000166</v>
@@ -10051,11 +10936,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W314" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="315" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W314" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X314" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="315" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P315" s="3">
         <f t="shared" si="24"/>
         <v>30.800000000000168</v>
@@ -10082,11 +10970,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W315" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="316" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W315" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X315" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="316" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P316" s="3">
         <f t="shared" si="24"/>
         <v>30.900000000000169</v>
@@ -10113,11 +11004,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W316" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="317" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W316" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X316" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="317" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P317" s="3">
         <f t="shared" si="24"/>
         <v>31.000000000000171</v>
@@ -10144,11 +11038,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W317" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="318" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W317" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X317" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="318" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P318" s="3">
         <f t="shared" si="24"/>
         <v>31.100000000000172</v>
@@ -10175,11 +11072,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W318" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="319" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W318" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X318" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="319" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P319" s="3">
         <f t="shared" si="24"/>
         <v>31.200000000000173</v>
@@ -10206,11 +11106,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W319" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="320" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W319" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X319" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="320" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P320" s="3">
         <f t="shared" si="24"/>
         <v>31.300000000000175</v>
@@ -10237,11 +11140,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W320" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="321" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W320" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X320" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="321" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P321" s="3">
         <f t="shared" si="24"/>
         <v>31.400000000000176</v>
@@ -10268,11 +11174,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W321" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="322" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W321" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X321" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="322" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P322" s="3">
         <f t="shared" si="24"/>
         <v>31.500000000000178</v>
@@ -10299,11 +11208,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W322" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="323" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W322" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X322" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="323" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P323" s="3">
         <f t="shared" si="24"/>
         <v>31.600000000000179</v>
@@ -10330,11 +11242,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W323" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="324" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W323" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X323" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="324" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P324" s="3">
         <f t="shared" si="24"/>
         <v>31.70000000000018</v>
@@ -10361,11 +11276,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W324" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="325" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W324" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X324" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="325" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P325" s="3">
         <f t="shared" si="24"/>
         <v>31.800000000000182</v>
@@ -10392,11 +11310,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W325" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="326" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W325" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X325" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="326" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P326" s="3">
         <f t="shared" si="24"/>
         <v>31.900000000000183</v>
@@ -10423,11 +11344,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W326" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="327" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W326" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X326" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="327" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P327" s="3">
         <f t="shared" si="24"/>
         <v>32.000000000000185</v>
@@ -10454,11 +11378,14 @@
         <f t="shared" si="23"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W327" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="328" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W327" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X327" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="328" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P328" s="3">
         <f t="shared" si="24"/>
         <v>32.100000000000186</v>
@@ -10485,11 +11412,14 @@
         <f t="shared" ref="V328:V391" si="28">(Q328*$Q$4+R328*$R$4)*(1+$S$5)</f>
         <v>32.199999999999996</v>
       </c>
-      <c r="W328" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="329" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W328" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X328" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="329" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P329" s="3">
         <f t="shared" ref="P329:P392" si="29">0.1+P328</f>
         <v>32.200000000000188</v>
@@ -10516,11 +11446,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W329" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="330" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W329" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X329" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="330" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P330" s="3">
         <f t="shared" si="29"/>
         <v>32.300000000000189</v>
@@ -10547,11 +11480,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W330" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="331" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W330" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X330" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="331" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P331" s="3">
         <f t="shared" si="29"/>
         <v>32.40000000000019</v>
@@ -10578,11 +11514,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W331" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="332" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W331" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X331" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="332" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P332" s="3">
         <f t="shared" si="29"/>
         <v>32.500000000000192</v>
@@ -10609,11 +11548,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W332" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="333" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W332" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X332" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="333" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P333" s="3">
         <f t="shared" si="29"/>
         <v>32.600000000000193</v>
@@ -10640,11 +11582,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W333" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="334" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W333" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X333" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="334" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P334" s="3">
         <f t="shared" si="29"/>
         <v>32.700000000000195</v>
@@ -10671,11 +11616,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W334" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="335" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W334" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X334" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="335" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P335" s="3">
         <f t="shared" si="29"/>
         <v>32.800000000000196</v>
@@ -10702,11 +11650,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W335" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="336" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W335" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X335" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="336" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P336" s="3">
         <f t="shared" si="29"/>
         <v>32.900000000000198</v>
@@ -10733,11 +11684,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W336" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="337" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W336" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X336" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="337" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P337" s="3">
         <f t="shared" si="29"/>
         <v>33.000000000000199</v>
@@ -10764,11 +11718,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W337" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="338" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W337" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X337" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="338" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P338" s="3">
         <f t="shared" si="29"/>
         <v>33.1000000000002</v>
@@ -10795,11 +11752,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W338" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="339" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W338" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X338" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="339" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P339" s="3">
         <f t="shared" si="29"/>
         <v>33.200000000000202</v>
@@ -10826,11 +11786,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W339" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="340" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W339" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X339" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="340" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P340" s="3">
         <f t="shared" si="29"/>
         <v>33.300000000000203</v>
@@ -10857,11 +11820,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W340" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="341" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W340" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X340" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="341" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P341" s="3">
         <f t="shared" si="29"/>
         <v>33.400000000000205</v>
@@ -10888,11 +11854,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W341" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="342" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W341" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X341" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="342" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P342" s="3">
         <f t="shared" si="29"/>
         <v>33.500000000000206</v>
@@ -10919,11 +11888,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W342" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="343" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W342" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X342" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="343" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P343" s="3">
         <f t="shared" si="29"/>
         <v>33.600000000000207</v>
@@ -10950,11 +11922,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W343" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="344" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W343" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X343" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="344" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P344" s="3">
         <f t="shared" si="29"/>
         <v>33.700000000000209</v>
@@ -10981,11 +11956,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W344" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="345" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W344" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X344" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="345" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P345" s="3">
         <f t="shared" si="29"/>
         <v>33.80000000000021</v>
@@ -11012,11 +11990,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W345" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="346" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W345" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X345" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="346" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P346" s="3">
         <f t="shared" si="29"/>
         <v>33.900000000000212</v>
@@ -11043,11 +12024,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W346" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="347" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W346" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X346" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="347" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P347" s="3">
         <f t="shared" si="29"/>
         <v>34.000000000000213</v>
@@ -11074,11 +12058,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W347" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="348" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W347" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X347" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="348" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P348" s="3">
         <f t="shared" si="29"/>
         <v>34.100000000000215</v>
@@ -11105,11 +12092,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W348" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="349" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W348" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X348" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="349" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P349" s="3">
         <f t="shared" si="29"/>
         <v>34.200000000000216</v>
@@ -11136,11 +12126,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W349" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="350" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W349" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X349" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="350" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P350" s="3">
         <f t="shared" si="29"/>
         <v>34.300000000000217</v>
@@ -11167,11 +12160,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W350" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="351" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W350" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X350" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="351" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P351" s="3">
         <f t="shared" si="29"/>
         <v>34.400000000000219</v>
@@ -11198,11 +12194,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W351" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="352" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W351" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X351" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="352" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P352" s="3">
         <f t="shared" si="29"/>
         <v>34.50000000000022</v>
@@ -11229,11 +12228,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W352" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="353" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W352" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X352" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="353" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P353" s="3">
         <f t="shared" si="29"/>
         <v>34.600000000000222</v>
@@ -11260,11 +12262,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W353" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="354" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W353" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X353" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="354" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P354" s="3">
         <f t="shared" si="29"/>
         <v>34.700000000000223</v>
@@ -11291,11 +12296,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W354" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="355" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W354" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X354" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="355" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P355" s="3">
         <f t="shared" si="29"/>
         <v>34.800000000000225</v>
@@ -11322,11 +12330,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W355" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="356" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W355" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X355" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="356" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P356" s="3">
         <f t="shared" si="29"/>
         <v>34.900000000000226</v>
@@ -11353,11 +12364,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W356" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="357" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W356" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X356" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="357" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P357" s="3">
         <f t="shared" si="29"/>
         <v>35.000000000000227</v>
@@ -11384,11 +12398,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W357" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="358" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W357" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X357" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="358" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P358" s="3">
         <f t="shared" si="29"/>
         <v>35.100000000000229</v>
@@ -11415,11 +12432,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W358" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="359" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W358" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X358" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="359" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P359" s="3">
         <f t="shared" si="29"/>
         <v>35.20000000000023</v>
@@ -11446,11 +12466,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W359" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="360" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W359" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X359" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="360" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P360" s="3">
         <f t="shared" si="29"/>
         <v>35.300000000000232</v>
@@ -11477,11 +12500,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W360" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="361" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W360" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X360" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="361" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P361" s="3">
         <f t="shared" si="29"/>
         <v>35.400000000000233</v>
@@ -11508,11 +12534,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W361" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="362" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W361" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X361" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="362" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P362" s="3">
         <f t="shared" si="29"/>
         <v>35.500000000000234</v>
@@ -11539,11 +12568,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W362" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="363" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W362" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X362" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="363" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P363" s="3">
         <f t="shared" si="29"/>
         <v>35.600000000000236</v>
@@ -11570,11 +12602,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W363" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="364" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W363" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X363" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="364" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P364" s="3">
         <f t="shared" si="29"/>
         <v>35.700000000000237</v>
@@ -11601,11 +12636,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W364" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="365" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W364" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X364" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="365" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P365" s="3">
         <f t="shared" si="29"/>
         <v>35.800000000000239</v>
@@ -11632,11 +12670,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W365" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="366" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W365" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X365" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="366" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P366" s="3">
         <f t="shared" si="29"/>
         <v>35.90000000000024</v>
@@ -11663,11 +12704,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W366" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="367" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W366" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X366" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="367" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P367" s="3">
         <f t="shared" si="29"/>
         <v>36.000000000000242</v>
@@ -11694,11 +12738,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W367" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="368" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W367" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X367" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="368" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P368" s="3">
         <f t="shared" si="29"/>
         <v>36.100000000000243</v>
@@ -11725,11 +12772,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W368" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="369" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W368" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X368" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="369" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P369" s="3">
         <f t="shared" si="29"/>
         <v>36.200000000000244</v>
@@ -11756,11 +12806,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W369" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="370" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W369" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X369" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="370" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P370" s="3">
         <f t="shared" si="29"/>
         <v>36.300000000000246</v>
@@ -11787,11 +12840,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W370" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="371" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W370" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X370" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="371" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P371" s="3">
         <f t="shared" si="29"/>
         <v>36.400000000000247</v>
@@ -11818,11 +12874,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W371" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="372" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W371" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X371" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="372" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P372" s="3">
         <f t="shared" si="29"/>
         <v>36.500000000000249</v>
@@ -11849,11 +12908,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W372" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="373" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W372" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X372" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="373" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P373" s="3">
         <f t="shared" si="29"/>
         <v>36.60000000000025</v>
@@ -11880,11 +12942,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W373" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="374" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W373" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X373" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="374" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P374" s="3">
         <f t="shared" si="29"/>
         <v>36.700000000000252</v>
@@ -11911,11 +12976,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W374" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="375" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W374" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X374" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="375" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P375" s="3">
         <f t="shared" si="29"/>
         <v>36.800000000000253</v>
@@ -11942,11 +13010,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W375" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="376" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W375" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X375" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="376" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P376" s="3">
         <f t="shared" si="29"/>
         <v>36.900000000000254</v>
@@ -11973,11 +13044,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W376" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="377" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W376" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X376" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="377" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P377" s="3">
         <f t="shared" si="29"/>
         <v>37.000000000000256</v>
@@ -12004,11 +13078,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W377" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="378" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W377" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X377" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="378" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P378" s="3">
         <f t="shared" si="29"/>
         <v>37.100000000000257</v>
@@ -12035,11 +13112,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W378" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="379" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W378" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X378" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="379" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P379" s="3">
         <f t="shared" si="29"/>
         <v>37.200000000000259</v>
@@ -12066,11 +13146,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W379" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="380" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W379" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X379" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="380" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P380" s="3">
         <f t="shared" si="29"/>
         <v>37.30000000000026</v>
@@ -12097,11 +13180,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W380" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="381" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W380" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X380" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="381" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P381" s="3">
         <f t="shared" si="29"/>
         <v>37.400000000000261</v>
@@ -12128,11 +13214,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W381" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="382" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W381" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X381" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="382" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P382" s="3">
         <f t="shared" si="29"/>
         <v>37.500000000000263</v>
@@ -12159,11 +13248,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W382" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="383" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W382" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X382" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="383" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P383" s="3">
         <f t="shared" si="29"/>
         <v>37.600000000000264</v>
@@ -12190,11 +13282,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W383" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="384" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W383" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X383" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="384" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P384" s="3">
         <f t="shared" si="29"/>
         <v>37.700000000000266</v>
@@ -12221,11 +13316,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W384" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="385" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W384" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X384" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="385" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P385" s="3">
         <f t="shared" si="29"/>
         <v>37.800000000000267</v>
@@ -12252,11 +13350,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W385" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="386" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W385" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X385" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="386" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P386" s="3">
         <f t="shared" si="29"/>
         <v>37.900000000000269</v>
@@ -12283,11 +13384,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W386" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="387" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W386" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X386" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="387" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P387" s="3">
         <f t="shared" si="29"/>
         <v>38.00000000000027</v>
@@ -12314,11 +13418,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W387" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="388" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W387" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X387" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="388" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P388" s="3">
         <f t="shared" si="29"/>
         <v>38.100000000000271</v>
@@ -12345,11 +13452,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W388" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="389" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W388" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X388" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="389" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P389" s="3">
         <f t="shared" si="29"/>
         <v>38.200000000000273</v>
@@ -12376,11 +13486,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W389" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="390" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W389" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X389" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="390" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P390" s="3">
         <f t="shared" si="29"/>
         <v>38.300000000000274</v>
@@ -12407,11 +13520,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W390" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="391" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W390" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X390" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="391" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P391" s="3">
         <f t="shared" si="29"/>
         <v>38.400000000000276</v>
@@ -12438,11 +13554,14 @@
         <f t="shared" si="28"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W391" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="392" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W391" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X391" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="392" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P392" s="3">
         <f t="shared" si="29"/>
         <v>38.500000000000277</v>
@@ -12469,11 +13588,14 @@
         <f t="shared" ref="V392:V420" si="33">(Q392*$Q$4+R392*$R$4)*(1+$S$5)</f>
         <v>32.199999999999996</v>
       </c>
-      <c r="W392" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="393" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W392" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X392" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="393" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P393" s="3">
         <f t="shared" ref="P393:P420" si="34">0.1+P392</f>
         <v>38.600000000000279</v>
@@ -12500,11 +13622,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W393" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="394" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W393" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X393" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="394" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P394" s="3">
         <f t="shared" si="34"/>
         <v>38.70000000000028</v>
@@ -12531,11 +13656,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W394" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="395" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W394" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X394" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="395" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P395" s="3">
         <f t="shared" si="34"/>
         <v>38.800000000000281</v>
@@ -12562,11 +13690,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W395" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="396" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W395" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X395" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="396" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P396" s="3">
         <f t="shared" si="34"/>
         <v>38.900000000000283</v>
@@ -12593,11 +13724,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W396" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="397" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W396" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X396" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="397" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P397" s="3">
         <f t="shared" si="34"/>
         <v>39.000000000000284</v>
@@ -12624,11 +13758,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W397" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="398" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W397" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X397" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="398" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P398" s="3">
         <f t="shared" si="34"/>
         <v>39.100000000000286</v>
@@ -12655,11 +13792,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W398" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="399" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W398" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X398" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="399" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P399" s="3">
         <f t="shared" si="34"/>
         <v>39.200000000000287</v>
@@ -12686,11 +13826,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W399" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="400" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W399" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X399" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="400" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P400" s="3">
         <f t="shared" si="34"/>
         <v>39.300000000000288</v>
@@ -12717,11 +13860,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W400" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="401" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W400" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X400" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="401" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P401" s="3">
         <f t="shared" si="34"/>
         <v>39.40000000000029</v>
@@ -12748,11 +13894,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W401" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="402" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W401" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X401" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="402" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P402" s="3">
         <f t="shared" si="34"/>
         <v>39.500000000000291</v>
@@ -12779,11 +13928,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W402" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="403" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W402" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X402" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="403" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P403" s="3">
         <f t="shared" si="34"/>
         <v>39.600000000000293</v>
@@ -12810,11 +13962,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W403" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="404" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W403" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X403" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="404" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P404" s="3">
         <f t="shared" si="34"/>
         <v>39.700000000000294</v>
@@ -12841,11 +13996,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W404" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="405" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W404" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X404" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="405" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P405" s="3">
         <f t="shared" si="34"/>
         <v>39.800000000000296</v>
@@ -12872,11 +14030,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W405" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="406" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W405" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X405" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="406" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P406" s="3">
         <f t="shared" si="34"/>
         <v>39.900000000000297</v>
@@ -12903,11 +14064,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W406" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="407" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W406" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X406" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="407" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P407" s="3">
         <f t="shared" si="34"/>
         <v>40.000000000000298</v>
@@ -12934,11 +14098,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W407" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="408" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W407" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X407" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="408" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P408" s="3">
         <f t="shared" si="34"/>
         <v>40.1000000000003</v>
@@ -12965,11 +14132,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W408" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="409" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W408" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X408" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="409" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P409" s="3">
         <f t="shared" si="34"/>
         <v>40.200000000000301</v>
@@ -12996,11 +14166,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W409" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="410" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W409" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X409" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="410" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P410" s="3">
         <f t="shared" si="34"/>
         <v>40.300000000000303</v>
@@ -13027,11 +14200,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W410" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="411" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W410" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X410" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="411" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P411" s="3">
         <f t="shared" si="34"/>
         <v>40.400000000000304</v>
@@ -13058,11 +14234,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W411" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="412" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W411" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X411" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="412" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P412" s="3">
         <f t="shared" si="34"/>
         <v>40.500000000000306</v>
@@ -13089,11 +14268,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W412" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="413" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W412" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X412" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="413" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P413" s="3">
         <f t="shared" si="34"/>
         <v>40.600000000000307</v>
@@ -13120,11 +14302,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W413" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="414" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W413" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X413" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="414" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P414" s="3">
         <f t="shared" si="34"/>
         <v>40.700000000000308</v>
@@ -13151,11 +14336,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W414" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="415" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W414" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X414" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="415" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P415" s="3">
         <f t="shared" si="34"/>
         <v>40.80000000000031</v>
@@ -13182,11 +14370,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W415" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="416" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W415" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X415" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="416" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P416" s="3">
         <f t="shared" si="34"/>
         <v>40.900000000000311</v>
@@ -13213,11 +14404,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W416" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="417" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W416" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X416" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="417" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P417" s="3">
         <f t="shared" si="34"/>
         <v>41.000000000000313</v>
@@ -13244,11 +14438,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W417" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="418" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W417" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X417" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="418" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P418" s="3">
         <f t="shared" si="34"/>
         <v>41.100000000000314</v>
@@ -13275,11 +14472,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W418" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="419" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W418" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X418" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="419" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P419" s="3">
         <f t="shared" si="34"/>
         <v>41.200000000000315</v>
@@ -13306,11 +14506,14 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W419" s="6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="420" spans="16:23" x14ac:dyDescent="0.3">
+      <c r="W419" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X419" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="420" spans="16:24" x14ac:dyDescent="0.25">
       <c r="P420" s="3">
         <f t="shared" si="34"/>
         <v>41.300000000000317</v>
@@ -13337,8 +14540,11 @@
         <f t="shared" si="33"/>
         <v>32.199999999999996</v>
       </c>
-      <c r="W420" s="6">
-        <v>3</v>
+      <c r="W420" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="X420" s="6">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
